--- a/outputs/cinema-rag-values-2026-09-24/影院购退票与营业服务_优化版.xlsx
+++ b/outputs/cinema-rag-values-2026-09-24/影院购退票与营业服务_优化版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\development\AI-Project\outputs\cinema-rag-values-2026-09-24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53381AE-9A73-46B3-BE94-443ED53E43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52689409-4ED7-4A2E-BBFC-D34F069252E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="影院问答库" sheetId="1" r:id="rId1"/>
@@ -127,19 +127,10 @@
     <t>什么样的电影票可以退？退票需要满足什么条件？</t>
   </si>
   <si>
-    <t>已支付并出票的订单可在开场前申请退票。场次距离开场超过 30 分钟时可以提交申请；距离开场 30 分钟及以内不再受理。</t>
-  </si>
-  <si>
     <t>开场前多久不能退票？提前半小时还能退吗？</t>
   </si>
   <si>
-    <t>退票截止时间为开场前 30 分钟。距离开场超过 30 分钟可以申请；到达截止时间或更晚时，系统将无法办理。</t>
-  </si>
-  <si>
     <t>距离开场正好 30 分钟，还可以退票吗？</t>
-  </si>
-  <si>
-    <t>不可以。退票需要在开场前 30 分钟以上提交；正好 30 分钟已到退票截止时间。</t>
   </si>
   <si>
     <t>电影已经开场还能退票吗？迟到后可以申请退款吗？</t>
@@ -415,6 +406,112 @@
   </si>
   <si>
     <t>两个人同时选中同一个座位会怎样？会不会重复卖票？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退票截止时间为开场前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分钟。距离开场超过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分钟可以申请；到达截止时间或更晚时，系统将无法办理。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已支付并出票的订单可在开场前申请退票。场次距离开场超过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分钟时可以提交申请；距离开场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF263238"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分钟及以内不再受理。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -422,7 +519,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -457,6 +554,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF263238"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -484,7 +588,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -493,6 +597,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -743,7 +850,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -798,7 +905,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -820,7 +927,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -910,8 +1017,8 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>35</v>
+      <c r="C17" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="24" customHeight="1">
@@ -919,10 +1026,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1">
@@ -930,10 +1037,10 @@
         <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
@@ -941,10 +1048,10 @@
         <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="24" customHeight="1">
@@ -952,428 +1059,428 @@
         <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="24" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="24" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="24" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
       <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C26" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="24" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="24" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="24" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="24" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="24" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="24" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C36" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="24" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="24" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="24" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="24" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="24" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="24" customHeight="1">
       <c r="A48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="24" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="24" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15" customHeight="1">
       <c r="A51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C51" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="24" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="36" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="24" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="24" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="24" customHeight="1">
       <c r="A56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="C56" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="24" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="24" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="24" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
